--- a/AAII_Financials/Yearly/BKU_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BKU_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>BKU</t>
   </si>
@@ -1007,11 +1007,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>636300</v>
+        <v>632500</v>
       </c>
       <c r="E17" s="3">
         <v>605900</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>388900</v>
+        <v>392700</v>
       </c>
       <c r="E18" s="3">
         <v>352500</v>
@@ -1254,7 +1254,7 @@
         <v>27200</v>
       </c>
       <c r="E20" s="3">
-        <v>36100</v>
+        <v>30900</v>
       </c>
       <c r="F20" s="3">
         <v>66700</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>376500</v>
+        <v>380300</v>
       </c>
       <c r="E21" s="3">
-        <v>334600</v>
+        <v>339800</v>
       </c>
       <c r="F21" s="3">
         <v>253400</v>
@@ -1866,7 +1866,7 @@
         <v>-27200</v>
       </c>
       <c r="E32" s="3">
-        <v>-36100</v>
+        <v>-30900</v>
       </c>
       <c r="F32" s="3">
         <v>-66700</v>
